--- a/output/Hubei/宜昌市_api_news.xlsx
+++ b/output/Hubei/宜昌市_api_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -543,13 +543,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>True</t>
@@ -561,13 +559,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -617,9 +615,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>True</t>
@@ -631,13 +627,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>36946</v>
+        <v>40484</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -687,9 +683,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>True</t>
@@ -701,13 +695,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -757,9 +751,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>True</t>
@@ -771,13 +763,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -823,13 +815,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>True</t>
@@ -841,7 +831,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -868,12 +858,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>疾控中心</t>
+          <t>宜昌市A级景区基本信息</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -883,23 +873,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>True</t>
@@ -911,7 +899,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -921,7 +909,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000478</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000908</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -938,12 +926,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>宜昌市A级景区基本信息</t>
+          <t>疾控中心</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -953,23 +941,21 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>True</t>
@@ -981,7 +967,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -991,7 +977,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000908</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000478</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1008,12 +994,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宜昌市博物馆一览表</t>
+          <t>宜昌城区停车场信息</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1023,23 +1009,21 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市城市管理执法委员会</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1051,17 +1035,17 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4051</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000917</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001392</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1078,12 +1062,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>急救机构基本信息</t>
+          <t>宜昌市博物馆一览表</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1093,23 +1077,21 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1121,17 +1103,17 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000616</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000917</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1148,12 +1130,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>宜昌城区停车场信息</t>
+          <t>急救机构基本信息</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1163,23 +1145,21 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>市城市管理执法委员会</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2023-03-02</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1191,17 +1171,17 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>3704</v>
+        <v>127</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001392</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000616</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1218,12 +1198,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>全市养老机构统计表</t>
+          <t>全市医疗卫生机构情况统计表</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1233,23 +1213,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2023-03-20</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1261,17 +1239,17 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>45109</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001396</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001393</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1288,7 +1266,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>西陵区人口统计统一识别码数据</t>
+          <t>全市养老机构统计表</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1303,23 +1281,21 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>True</t>
@@ -1331,22 +1307,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>49305</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001400</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001396</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1334,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>宜昌市非物质文化遗产省级传承人</t>
+          <t>西陵区人口统计统一识别码数据</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1373,23 +1349,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>True</t>
@@ -1401,22 +1375,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000927</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001400</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1402,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>宜昌市旅行社一览表</t>
+          <t>建设工程规划许可证</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1443,23 +1417,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市自然资源和城乡建设局</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1471,22 +1443,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000909</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000581</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1470,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全市医疗卫生机构情况统计表</t>
+          <t>宜昌市非物质文化遗产省级传承人</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1513,23 +1485,21 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2023-03-07</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1541,17 +1511,17 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001393</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000927</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1568,12 +1538,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>建设工程规划许可证</t>
+          <t>宜昌市旅行社一览表</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1583,23 +1553,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>市自然资源和规划局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>True</t>
@@ -1611,22 +1579,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000581</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000909</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -1667,9 +1635,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>True</t>
@@ -1681,7 +1647,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1737,9 +1703,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>True</t>
@@ -1751,13 +1715,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1807,9 +1771,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>True</t>
@@ -1821,13 +1783,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1122</v>
+        <v>1256</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1848,12 +1810,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>劳务派遣企业名单信息</t>
+          <t>全市婚姻登记机构</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>居民服务、修理和其他服务业</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1863,7 +1825,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>市人力资源和社会保障局</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1873,13 +1835,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>True</t>
@@ -1891,17 +1851,17 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000636</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000710</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1918,12 +1878,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>宜昌市水库安全（防汛）管理责任人名单</t>
+          <t>劳务派遣企业名单信息</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1933,7 +1893,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>市水利和湖泊局</t>
+          <t>市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1943,13 +1903,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>True</t>
@@ -1961,7 +1919,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1971,7 +1929,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000469</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000636</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1988,12 +1946,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>加油站企业名单</t>
+          <t>宜昌市水库安全（防汛）管理责任人名单</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>批发和零售业</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2003,7 +1961,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>市商务局</t>
+          <t>市水利和湖泊局</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2013,13 +1971,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>True</t>
@@ -2031,22 +1987,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000442</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000469</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2014,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>星级养老机构</t>
+          <t>加油站企业名单</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>居民服务、修理和其他服务业</t>
+          <t>批发和零售业</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2073,7 +2029,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市商务局</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2083,13 +2039,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2101,22 +2055,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1051</v>
+        <v>19</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000702</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000442</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2082,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>宜昌市人社局电话咨询专线</t>
+          <t>星级养老机构</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>居民服务、修理和其他服务业</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2143,23 +2097,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>市人力资源和社会保障局</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2171,17 +2123,17 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1063</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001130</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000702</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2198,12 +2150,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>宜昌市全国重点文物保护单位</t>
+          <t>宜昌市人社局电话咨询专线</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2213,23 +2165,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>True</t>
@@ -2241,7 +2191,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2251,7 +2201,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000914</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001130</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2268,12 +2218,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>危险化学品经营许可登记表</t>
+          <t>宜昌市全国重点文物保护单位</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2283,23 +2233,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>市应急管理局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>True</t>
@@ -2311,17 +2259,17 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000562</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000914</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2338,12 +2286,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>全市婚姻登记机构</t>
+          <t>危险化学品经营许可登记表</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>居民服务、修理和其他服务业</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2353,7 +2301,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市应急管理局</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2363,13 +2311,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>True</t>
@@ -2381,17 +2327,17 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>557</v>
-      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000710</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000562</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2423,7 +2369,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>市自然资源和规划局</t>
+          <t>市自然资源和城乡建设局</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2437,9 +2383,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>True</t>
@@ -2451,7 +2395,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2507,9 +2451,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>True</t>
@@ -2521,7 +2463,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2577,9 +2519,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>True</t>
@@ -2591,7 +2531,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2643,13 +2583,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>True</t>
@@ -2661,7 +2599,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M32" t="n">
         <v>2</v>
@@ -2717,9 +2655,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>True</t>
@@ -2731,7 +2667,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2787,9 +2723,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>True</t>
@@ -2801,7 +2735,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2857,9 +2791,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>True</t>
@@ -2871,7 +2803,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2927,9 +2859,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>True</t>
@@ -2941,13 +2871,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>1319</v>
+        <v>1445</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2983,7 +2913,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2997,9 +2927,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>True</t>
@@ -3011,7 +2939,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3067,9 +2995,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3081,7 +3007,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3137,9 +3063,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>True</t>
@@ -3151,7 +3075,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3207,9 +3131,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>True</t>
@@ -3221,13 +3143,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>5208</v>
+        <v>5975</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3277,9 +3199,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>True</t>
@@ -3291,7 +3211,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3347,9 +3267,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>True</t>
@@ -3361,7 +3279,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3417,9 +3335,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>True</t>
@@ -3431,7 +3347,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3487,9 +3403,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>True</t>
@@ -3501,7 +3415,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3557,9 +3471,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>True</t>
@@ -3571,7 +3483,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -3627,9 +3539,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>True</t>
@@ -3641,13 +3551,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>2012</v>
+        <v>2105</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3668,12 +3578,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>利用公共资源建设的景区门票价格</t>
+          <t>县市区民政局</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>居民服务、修理和其他服务业</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3683,7 +3593,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>市发展和改革委员会</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3693,13 +3603,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>True</t>
@@ -3711,17 +3619,17 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2590</v>
+        <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000367</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000698</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3738,12 +3646,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>基金会信息</t>
+          <t>利用公共资源建设的景区门票价格</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3753,7 +3661,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市发展和改革委员会</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3763,13 +3671,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>True</t>
@@ -3781,17 +3687,17 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2777</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000714</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000367</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3808,7 +3714,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>社会组织年检信息</t>
+          <t>基金会信息</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3833,13 +3739,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>True</t>
@@ -3851,7 +3755,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3861,12 +3765,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000716</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000714</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3782,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>社会团体变更信息</t>
+          <t>社会组织年检信息</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3903,13 +3807,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>True</t>
@@ -3921,7 +3823,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3931,12 +3833,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000718</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000716</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3850,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>民办非企业单位变更信息</t>
+          <t>社会团体变更信息</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3977,9 +3879,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>True</t>
@@ -3991,7 +3891,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -4001,7 +3901,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000719</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000718</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4018,7 +3918,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>社会组织注销信息</t>
+          <t>民办非企业单位变更信息</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4047,9 +3947,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>True</t>
@@ -4061,7 +3959,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -4071,7 +3969,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000720</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000719</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -4088,12 +3986,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>水库基础信息</t>
+          <t>社会组织注销信息</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4103,23 +4001,21 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>市水利和湖泊局</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>True</t>
@@ -4131,7 +4027,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -4141,12 +4037,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001655</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000720</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4054,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>全市普通机动车驾驶员培训企业名录</t>
+          <t>水库基础信息</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4173,23 +4069,21 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>市交通运输局</t>
+          <t>市水利和湖泊局</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>True</t>
@@ -4201,7 +4095,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -4211,12 +4105,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000402</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001655</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4122,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>宜昌市机动车登记服务站</t>
+          <t>全市普通机动车驾驶员培训企业名录</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4243,23 +4137,21 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>市公安局交通警察支队</t>
+          <t>市交通运输局</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>True</t>
@@ -4271,7 +4163,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4281,7 +4173,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001147</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000402</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4298,12 +4190,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>宜昌市号门牌地址统一识别码数据</t>
+          <t>宜昌市机动车登记服务站</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4313,23 +4205,21 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市公安局交通警察支队</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>True</t>
@@ -4341,7 +4231,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -4351,12 +4241,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001401</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001147</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4258,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>公共就业服务机构信息</t>
+          <t>宜昌市号门牌地址统一识别码数据</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4383,23 +4273,21 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>市人力资源和社会保障局</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>True</t>
@@ -4411,7 +4299,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -4421,12 +4309,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000618</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001401</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4326,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2022年保障性租赁住房筹集计划项目清单</t>
+          <t>公共就业服务机构信息</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4453,23 +4341,21 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>True</t>
@@ -4481,7 +4367,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -4491,12 +4377,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001138</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000618</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>不更新</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4394,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>出租车公司电话一览表</t>
+          <t>2022年保障性租赁住房筹集计划项目清单</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4523,23 +4409,21 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>市交通运输局</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2023-11-27</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>True</t>
@@ -4551,7 +4435,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -4561,12 +4445,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000395</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001138</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>不更新</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4462,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>民办技工学校信息</t>
+          <t>出租车公司电话一览表</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4593,7 +4477,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>市人力资源和社会保障局</t>
+          <t>市交通运输局</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4603,13 +4487,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>True</t>
@@ -4621,7 +4503,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4631,7 +4513,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000639</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000395</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -4648,12 +4530,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>车管服务网点</t>
+          <t>民办技工学校信息</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>居民服务、修理和其他服务业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4663,7 +4545,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>市公安局交通警察支队</t>
+          <t>市人力资源和社会保障局</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4673,13 +4555,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>True</t>
@@ -4691,7 +4571,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -4701,7 +4581,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000728</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000639</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4718,7 +4598,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>机动车检测机构</t>
+          <t>车管服务网点</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4747,9 +4627,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>True</t>
@@ -4761,17 +4639,17 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000741</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000728</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -4788,12 +4666,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>产业技术研究院目录信息</t>
+          <t>机动车检测机构</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>科学研究和技术服务业</t>
+          <t>居民服务、修理和其他服务业</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4803,7 +4681,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>市科学技术局</t>
+          <t>市公安局交通警察支队</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4813,13 +4691,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>True</t>
@@ -4831,22 +4707,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000428</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000741</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4734,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>国际合作基地</t>
+          <t>产业技术研究院目录信息</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4887,9 +4763,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>True</t>
@@ -4901,7 +4775,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -4911,12 +4785,12 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000435</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000428</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4802,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>宜昌市市级文物保护单位</t>
+          <t>国际合作基地</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>科学研究和技术服务业</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4943,23 +4817,21 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市科学技术局</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>True</t>
@@ -4971,7 +4843,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -4981,7 +4853,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000912</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000435</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -4998,7 +4870,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>宜昌市省级文物保护单位</t>
+          <t>宜昌市市级文物保护单位</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5023,13 +4895,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>True</t>
@@ -5041,7 +4911,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5051,7 +4921,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000910</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000912</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5068,7 +4938,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>宜昌市市级非物质文化遗产代表性项目名录列表</t>
+          <t>宜昌市省级文物保护单位</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5097,9 +4967,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>True</t>
@@ -5111,7 +4979,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -5121,7 +4989,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000915</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000910</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5138,7 +5006,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>宜昌市美术馆一览表</t>
+          <t>宜昌市市级非物质文化遗产代表性项目名录列表</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5163,13 +5031,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>True</t>
@@ -5181,7 +5047,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5191,7 +5057,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000916</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000915</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5208,7 +5074,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>宜昌市文化馆一览表</t>
+          <t>宜昌市美术馆一览表</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5237,9 +5103,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>True</t>
@@ -5251,7 +5115,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5261,7 +5125,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000918</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000916</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5278,7 +5142,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>宜昌市非物质文化遗产市级传承人</t>
+          <t>宜昌市文化馆一览表</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5303,13 +5167,11 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>True</t>
@@ -5321,7 +5183,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5331,7 +5193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000922</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000918</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -5348,7 +5210,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>宜昌市国家级非物质文化遗产代表性项目名录列表</t>
+          <t>宜昌市非物质文化遗产市级传承人</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5377,9 +5239,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>True</t>
@@ -5391,7 +5251,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -5401,7 +5261,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000924</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000922</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5418,7 +5278,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>宜昌市出境旅游旅行社一览表</t>
+          <t>宜昌市国家级非物质文化遗产代表性项目名录列表</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5447,9 +5307,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>True</t>
@@ -5461,7 +5319,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -5471,7 +5329,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000925</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000924</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -5488,12 +5346,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>基层法律服务人员信息</t>
+          <t>宜昌市出境旅游旅行社一览表</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>公共管理、社会保障和社会组织</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5503,23 +5361,21 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>市司法局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>True</t>
@@ -5531,7 +5387,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -5541,7 +5397,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000655</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000925</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5558,7 +5414,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>基层法律服务机构信息</t>
+          <t>基层法律服务人员信息</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5583,13 +5439,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>True</t>
@@ -5601,7 +5455,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -5611,7 +5465,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000656</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000655</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5628,7 +5482,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>司法鉴定机构信息</t>
+          <t>基层法律服务机构信息</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5653,13 +5507,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2022-11-28</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>True</t>
@@ -5671,7 +5523,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -5681,7 +5533,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000665</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000656</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5698,7 +5550,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>律师信息</t>
+          <t>司法鉴定机构信息</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5723,13 +5575,11 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
+          <t>2022-11-28</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>True</t>
@@ -5741,7 +5591,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5751,7 +5601,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000668</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000665</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -5768,7 +5618,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>公安窗口地址电话</t>
+          <t>律师信息</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5783,7 +5633,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>市公安局</t>
+          <t>市司法局</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5793,13 +5643,11 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2022-12-05</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>True</t>
@@ -5811,7 +5659,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -5821,7 +5669,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000750</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000668</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5838,12 +5686,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>县市区民政局</t>
+          <t>公安窗口地址电话</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>居民服务、修理和其他服务业</t>
+          <t>公共管理、社会保障和社会组织</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5853,7 +5701,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市公安局</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5863,13 +5711,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>True</t>
@@ -5881,7 +5727,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -5891,7 +5737,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000698</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000750</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -5937,9 +5783,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>True</t>
@@ -5951,7 +5795,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M79" t="n">
         <v>1</v>
@@ -6007,9 +5851,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>True</t>
@@ -6021,7 +5863,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -6048,7 +5890,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>乡村游</t>
+          <t>打卡地</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6073,13 +5915,11 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>True</t>
@@ -6091,7 +5931,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -6101,7 +5941,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001632</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001629</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -6118,7 +5958,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>宾馆</t>
+          <t>乡村游</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6143,13 +5983,11 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>True</t>
@@ -6161,7 +5999,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -6171,7 +6009,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001640</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001632</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -6188,12 +6026,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>流域基础信息</t>
+          <t>宾馆</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6203,23 +6041,21 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>市水利和湖泊局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>True</t>
@@ -6231,7 +6067,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -6241,7 +6077,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001645</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001640</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -6258,12 +6094,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>全市社区居家养老服务中心（站）</t>
+          <t>流域基础信息</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>居民服务、修理和其他服务业</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6273,23 +6109,21 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>市民政局</t>
+          <t>市水利和湖泊局</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>True</t>
@@ -6301,22 +6135,22 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001690</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001645</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -6328,12 +6162,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>民宿</t>
+          <t>全市社区居家养老服务中心（站）</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>居民服务、修理和其他服务业</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6343,23 +6177,21 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市民政局</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>True</t>
@@ -6371,22 +6203,22 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001639</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001690</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -6398,12 +6230,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>演出预告表</t>
+          <t>宜昌市预警信号数据</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6413,23 +6245,21 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市气象局</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>True</t>
@@ -6441,22 +6271,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001641</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001596</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>每日</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6298,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>打卡地</t>
+          <t>民宿</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6493,13 +6323,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>True</t>
@@ -6511,7 +6339,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -6521,7 +6349,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001629</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001639</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -6538,7 +6366,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>老字号</t>
+          <t>演出预告表</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6563,13 +6391,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>True</t>
@@ -6581,7 +6407,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -6591,7 +6417,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001630</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001641</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -6608,7 +6434,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>赏花地</t>
+          <t>老字号</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6633,13 +6459,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>True</t>
@@ -6651,7 +6475,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -6661,7 +6485,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001634</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001630</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -6678,12 +6502,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>倒虹吸基础信息</t>
+          <t>赏花地</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6693,23 +6517,21 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>市水利和湖泊局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>True</t>
@@ -6721,7 +6543,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -6731,7 +6553,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001652</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001634</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -6748,7 +6570,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>泵站基础信息</t>
+          <t>倒虹吸基础信息</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6773,13 +6595,11 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>True</t>
@@ -6791,7 +6611,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -6801,7 +6621,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001654</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001652</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -6818,12 +6638,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>全市医疗机构发热门诊（诊室）</t>
+          <t>泵站基础信息</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6833,23 +6653,21 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市水利和湖泊局</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>True</t>
@@ -6861,22 +6679,22 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001565</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001654</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -6888,12 +6706,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>宜昌市城区城市道路临时停车泊位清单</t>
+          <t>宜昌市星级饭店名录</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>住宿和餐饮业</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6903,23 +6721,21 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>市发展和改革委员会</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>True</t>
@@ -6931,17 +6747,17 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001563</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001478</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -6958,12 +6774,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>宜昌市预警信号数据</t>
+          <t>全市医疗机构发热门诊（诊室）</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6973,23 +6789,21 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>市气象局</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>True</t>
@@ -7001,22 +6815,22 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>236</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001596</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001565</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>每日</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -7028,12 +6842,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>公共场馆</t>
+          <t>宜昌市城区城市道路临时停车泊位清单</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7043,23 +6857,21 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市发展和改革委员会</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>True</t>
@@ -7071,22 +6883,22 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001638</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001563</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -7098,7 +6910,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>演出场馆表</t>
+          <t>公共场馆</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7123,13 +6935,11 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>True</t>
@@ -7141,7 +6951,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -7151,7 +6961,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001642</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001638</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -7168,7 +6978,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>文惠卡发行计划</t>
+          <t>演出场馆表</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7193,13 +7003,11 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>True</t>
@@ -7211,7 +7019,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -7221,7 +7029,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001643</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001642</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -7238,7 +7046,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>景区基本信息表</t>
+          <t>文惠卡发行计划</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7263,13 +7071,11 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>True</t>
@@ -7281,7 +7087,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -7291,7 +7097,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001631</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001643</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -7308,7 +7114,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>集散中心</t>
+          <t>景区基本信息表</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7333,13 +7139,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>True</t>
@@ -7351,7 +7155,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -7361,7 +7165,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001633</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001631</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -7378,7 +7182,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>采摘地</t>
+          <t>集散中心</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7403,13 +7207,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>True</t>
@@ -7421,7 +7223,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -7431,7 +7233,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001635</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001633</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -7448,7 +7250,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>民俗风情</t>
+          <t>采摘地</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7473,13 +7275,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>True</t>
@@ -7491,7 +7291,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -7501,7 +7301,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001636</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001635</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -7518,7 +7318,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>历史遗产</t>
+          <t>民俗风情</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7543,13 +7343,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>True</t>
@@ -7561,7 +7359,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -7571,7 +7369,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001637</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001636</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -7588,12 +7386,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>宜昌市城区城市道路临时停车泊位收费标准</t>
+          <t>历史遗产</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7603,23 +7401,21 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>市发展和改革委员会</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2023-02-14</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>True</t>
@@ -7631,22 +7427,22 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001365</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001637</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7454,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>河流基础信息</t>
+          <t>宜昌市城区城市道路临时停车泊位收费标准</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>水利、环境和公共设施管理业</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7673,23 +7469,21 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>市水利和湖泊局</t>
+          <t>市发展和改革委员会</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-02-14</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>True</t>
@@ -7701,22 +7495,22 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001646</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001365</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7522,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>灌区基础信息</t>
+          <t>河流基础信息</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7753,13 +7547,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>True</t>
@@ -7771,7 +7563,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -7781,7 +7573,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001653</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001646</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -7798,7 +7590,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>水库大坝基础信息</t>
+          <t>灌区基础信息</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7823,13 +7615,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>True</t>
@@ -7841,7 +7631,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -7851,7 +7641,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001656</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001653</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -7868,7 +7658,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>水闸基础信息表</t>
+          <t>水库大坝基础信息</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7893,13 +7683,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>True</t>
@@ -7911,7 +7699,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
@@ -7921,7 +7709,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001648</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001656</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -7938,7 +7726,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>引调水基础信息</t>
+          <t>采砂船泊停靠点</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7958,18 +7746,16 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>True</t>
@@ -7981,7 +7767,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -7991,7 +7777,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001649</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001658</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -8008,7 +7794,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>涵洞基础信息</t>
+          <t>水闸基础信息表</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8033,13 +7819,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>True</t>
@@ -8051,7 +7835,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -8061,7 +7845,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001650</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001648</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -8078,7 +7862,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>渡槽基础信息</t>
+          <t>引调水基础信息</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8103,13 +7887,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>True</t>
@@ -8121,7 +7903,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -8131,7 +7913,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001657</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001649</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -8148,7 +7930,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>采砂船泊停靠点</t>
+          <t>涵洞基础信息</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8168,18 +7950,16 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>True</t>
@@ -8191,7 +7971,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -8201,7 +7981,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001658</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001650</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8218,7 +7998,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>湖泊基础信息</t>
+          <t>渡槽基础信息</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8238,18 +8018,16 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>True</t>
@@ -8261,7 +8039,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -8271,12 +8049,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001659</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001657</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -8288,12 +8066,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>宜昌市星级饭店名录</t>
+          <t>湖泊基础信息</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>住宿和餐饮业</t>
+          <t>水利、环境和公共设施管理业</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8303,23 +8081,21 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市水利和湖泊局</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>True</t>
@@ -8331,22 +8107,22 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001478</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001659</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8134,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>航道信息表</t>
+          <t>宜昌市医院信息</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8373,23 +8149,21 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>市交通运输局</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>True</t>
@@ -8401,22 +8175,22 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>13894</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001607</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001691</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>每月</t>
+          <t>不定期</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8202,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>码头泊位信息</t>
+          <t>航道信息表</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8453,13 +8227,11 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>True</t>
@@ -8471,7 +8243,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -8481,7 +8253,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001609</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001607</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -8498,7 +8270,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>码头建设信息</t>
+          <t>码头泊位信息</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8523,13 +8295,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>True</t>
@@ -8541,7 +8311,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -8551,7 +8321,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001610</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001609</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -8568,12 +8338,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>非遗项目信息</t>
+          <t>码头建设信息</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>文化、体育和娱乐业</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8583,23 +8353,21 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>市文化和旅游局</t>
+          <t>市交通运输局</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>True</t>
@@ -8611,7 +8379,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
@@ -8621,12 +8389,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001606</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001610</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>每年</t>
+          <t>每月</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8406,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>机动车维修企业信息</t>
+          <t>非遗项目信息</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>交通运输、仓储和邮政业</t>
+          <t>文化、体育和娱乐业</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8653,23 +8421,21 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>市交通运输局</t>
+          <t>市文化和旅游局</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>True</t>
@@ -8681,22 +8447,22 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001558</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001606</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>不定期</t>
+          <t>每年</t>
         </is>
       </c>
     </row>
@@ -8708,12 +8474,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>宜昌市医院信息</t>
+          <t>机动车维修企业信息</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>交通运输、仓储和邮政业</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8723,23 +8489,21 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市交通运输局</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>True</t>
@@ -8751,17 +8515,17 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M119" t="n">
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>10713</v>
+        <v>43</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001691</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001558</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -8778,12 +8542,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>全市无偿献血站地点</t>
+          <t>宜昌市可供给保障性租赁住房房源信息表</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>卫生和社会工作</t>
+          <t>建筑业</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8793,23 +8557,21 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>市卫生健康委员会</t>
+          <t>市住房和城市更新局</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>True</t>
@@ -8821,17 +8583,17 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>65</v>
+        <v>515</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001599</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001562</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -8848,7 +8610,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>全市预防接种点信息</t>
+          <t>全市无偿献血站地点</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8868,7 +8630,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8877,9 +8639,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>True</t>
@@ -8891,17 +8651,17 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M121" t="n">
         <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>249</v>
+        <v>69</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001600</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001599</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -8918,12 +8678,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>宜昌市可供给保障性租赁住房房源信息表</t>
+          <t>全市预防接种点信息</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>建筑业</t>
+          <t>卫生和社会工作</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8933,23 +8693,21 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>市住房和城乡建设局</t>
+          <t>市卫生健康委员会</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>True</t>
@@ -8961,17 +8719,17 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M122" t="n">
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001562</t>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001600</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -9017,9 +8775,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>True</t>
@@ -9031,13 +8787,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -9087,9 +8843,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>True</t>
@@ -9101,13 +8855,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -9157,9 +8911,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>True</t>
@@ -9171,13 +8923,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M125" t="n">
         <v>1</v>
       </c>
       <c r="N125" t="n">
-        <v>213</v>
+        <v>317</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -9227,9 +8979,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>True</t>
@@ -9241,13 +8991,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M126" t="n">
         <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -9257,6 +9007,346 @@
       <c r="P126" t="inlineStr">
         <is>
           <t>不定期</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>宜昌市</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>各地区医疗卫生机构</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>卫生和社会工作</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>获取数据</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>市卫生健康委员会</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2021-12-15</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>['接口']</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1000481</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>不定期</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>宜昌市</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>工程建设_中标候选人公示</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>科学研究和技术服务业</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>获取数据</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>市公共资源交易中心</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>['接口']</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>2</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001680</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>每月</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>宜昌市</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2022年宜昌市重点排污单位名录</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>水利、环境和公共设施管理业</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>获取数据</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>市生态环境局</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2022-05-20</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>['接口']</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>2</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001210</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>宜昌市</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>市级制造业高质量发展专项资金拟支持项目名单</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>获取数据</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>市经济和信息化局</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2023-11-27</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>['接口']</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>2</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001302</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>每年</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>宜昌市</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>宜昌市天气预报信息</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>水利、环境和公共设施管理业</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>获取数据</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>市气象局</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2022-03-16</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>['接口']</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>2</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>https://data.yichang.gov.cn/kf/open/interface/detail/1001073</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>每日</t>
         </is>
       </c>
     </row>
